--- a/output/pdf_financials_xlsx/QPT.xlsx
+++ b/output/pdf_financials_xlsx/QPT.xlsx
@@ -994,13 +994,13 @@
         <v>0.834216</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.542861</v>
+        <v>1.31582</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.329181</v>
+        <v>0.817285</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.242324</v>
+        <v>0.711259</v>
       </c>
     </row>
     <row r="11">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.020159</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002522</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>8.500000000000001e-05</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.204047</v>
+        <v>-0.224206</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.517799</v>
+        <v>-0.520321</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.353858</v>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.204047</v>
+        <v>-0.224206</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.517799</v>
+        <v>-0.520321</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.353858</v>
@@ -2568,7 +2568,7 @@
         <v>0.013394</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.074975</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.056637</v>
@@ -2577,7 +2577,7 @@
         <v>0.742447</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.100042</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -2595,22 +2595,22 @@
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.199114</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.26434</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.374658</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.716963</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.205085</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.014363</v>
       </c>
     </row>
     <row r="35">
@@ -2690,7 +2690,7 @@
         <v>0.013394</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.074975</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.056637</v>
@@ -2699,7 +2699,7 @@
         <v>0.742447</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.100042</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
@@ -2717,22 +2717,22 @@
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.199114</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.26434</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.374658</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.716963</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.205085</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.014363</v>
       </c>
     </row>
     <row r="37">
@@ -3422,7 +3422,7 @@
         <v>0.09209000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.105559</v>
+        <v>0.030584</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.025582</v>
@@ -3431,7 +3431,7 @@
         <v>0.03448</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.223969</v>
+        <v>0.123927</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.865777</v>
@@ -3449,22 +3449,22 @@
         <v>2.877698</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.24872</v>
+        <v>0.049606</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.28783</v>
+        <v>0.02349</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.400191</v>
+        <v>0.025533</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.73553</v>
+        <v>0.018567</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.225279</v>
+        <v>0.020194</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.032881</v>
+        <v>0.018518</v>
       </c>
     </row>
     <row r="49">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -48546,7 +48546,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -78204,7 +78204,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E662" s="5" t="n">

--- a/output/pdf_financials_xlsx/QPT.xlsx
+++ b/output/pdf_financials_xlsx/QPT.xlsx
@@ -4031,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.061161</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.056656</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.0375</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -25488,7 +25488,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -44506,7 +44510,11 @@
           <t>Proceeds from sale of marketable securities [note 7]</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -45996,7 +46004,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -47696,7 +47708,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
